--- a/Issue 4B/HARLEQUIN 128 Issue 4B BOM.xlsx
+++ b/Issue 4B/HARLEQUIN 128 Issue 4B BOM.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Retro Computer\zx spectrum\_clone\superfo\128K\Issue 4\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43BD49A-715C-41F4-9C04-DE151F0BB9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18470" windowHeight="17240"/>
+    <workbookView xWindow="17840" yWindow="1390" windowWidth="19600" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HARLEQUIN 128 Issue 4" sheetId="1" r:id="rId1"/>
@@ -756,7 +757,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -988,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1031,7 +1032,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1466,7 +1466,7 @@
         <v>129</v>
       </c>
       <c r="D11" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.4">
@@ -1632,7 +1632,7 @@
       <c r="B24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="5" t="s">
         <v>239</v>
       </c>
       <c r="D24" s="19">
